--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484709_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484709_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.4222</v>
+        <v>4.4865</v>
       </c>
       <c r="E2" t="n">
-        <v>1.7827</v>
+        <v>1.9792</v>
       </c>
       <c r="F2" t="n">
-        <v>2.6395</v>
+        <v>2.5072</v>
       </c>
       <c r="G2" t="n">
         <v>-1.4196</v>
@@ -610,13 +610,13 @@
         <v>4.3401</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.4409</v>
+        <v>-0.3767</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.8419</v>
+        <v>-0.6454</v>
       </c>
       <c r="U2" t="n">
-        <v>0.401</v>
+        <v>0.2687</v>
       </c>
       <c r="V2" t="n">
         <v>4.9618</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.139</v>
+        <v>3.3561</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3496</v>
+        <v>0.4873</v>
       </c>
       <c r="F3" t="n">
-        <v>2.7894</v>
+        <v>2.8688</v>
       </c>
       <c r="G3" t="n">
         <v>0.7847</v>
@@ -688,13 +688,13 @@
         <v>3.9627</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.6649</v>
+        <v>-0.4478</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.6778999999999999</v>
+        <v>-0.5402</v>
       </c>
       <c r="U3" t="n">
-        <v>0.013</v>
+        <v>0.0924</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.5643</v>
+        <v>3.1951</v>
       </c>
       <c r="E4" t="n">
-        <v>1.3046</v>
+        <v>1.9883</v>
       </c>
       <c r="F4" t="n">
-        <v>1.2597</v>
+        <v>1.2068</v>
       </c>
       <c r="G4" t="n">
         <v>1.3563</v>
@@ -766,13 +766,13 @@
         <v>4.7175</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.415</v>
+        <v>-0.7842</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.7977</v>
+        <v>-1.1141</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3828</v>
+        <v>0.3299</v>
       </c>
       <c r="V4" t="n">
         <v>-0.9624</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. LAVRENOV</t>
+          <t>P. LOPEZ-VALVERDE CARRASCO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.7853</v>
+        <v>-0.7308</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.1052</v>
+        <v>-1.3648</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.68</v>
+        <v>0.634</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.5854</v>
+        <v>-0.704</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.7153</v>
+        <v>-1.7929</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1299</v>
+        <v>1.0889</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>2.3954</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>1.0041</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.3914</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.5854</v>
+        <v>-3.0994</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.7153</v>
+        <v>-2.797</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1299</v>
+        <v>-0.3024</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.4531</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-2.0757</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>4.5288</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1999</v>
+        <v>-0.5931</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1052</v>
+        <v>-1.0429</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0946</v>
+        <v>0.4498</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>-1.8868</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>-0.6415999999999999</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-1.2452</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>P. LOPEZ-VALVERDE CARRASCO</t>
+          <t>A. LAVRENOV</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.0176</v>
+        <v>-0.7323</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.0485</v>
+        <v>-0.1052</v>
       </c>
       <c r="F6" t="n">
-        <v>1.0308</v>
+        <v>-0.6271</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.704</v>
+        <v>-0.5854</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.7929</v>
+        <v>-0.7153</v>
       </c>
       <c r="I6" t="n">
-        <v>1.0889</v>
+        <v>0.1299</v>
       </c>
       <c r="J6" t="n">
-        <v>2.3954</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>1.0041</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>1.3914</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>-3.0994</v>
+        <v>-0.5854</v>
       </c>
       <c r="N6" t="n">
-        <v>-2.797</v>
+        <v>-0.7153</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.3024</v>
+        <v>0.1299</v>
       </c>
       <c r="P6" t="n">
-        <v>2.4531</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.0757</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>4.5288</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.88</v>
+        <v>-0.147</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.7266</v>
+        <v>-0.1052</v>
       </c>
       <c r="U6" t="n">
-        <v>0.8466</v>
+        <v>-0.0417</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.8868</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.6415999999999999</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.2452</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.2741</v>
+        <v>-1.0301</v>
       </c>
       <c r="E7" t="n">
-        <v>0.3258</v>
+        <v>0.3846</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.5999</v>
+        <v>-1.4147</v>
       </c>
       <c r="G7" t="n">
         <v>-1.1115</v>
@@ -1000,13 +1000,13 @@
         <v>1.6983</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.0305</v>
+        <v>-0.7866</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.9871</v>
+        <v>-0.9283</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0435</v>
+        <v>0.1417</v>
       </c>
       <c r="V7" t="n">
         <v>0.3018</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.4337</v>
+        <v>-2.5392</v>
       </c>
       <c r="E8" t="n">
-        <v>-3.6022</v>
+        <v>-3.8928</v>
       </c>
       <c r="F8" t="n">
-        <v>1.1684</v>
+        <v>1.3536</v>
       </c>
       <c r="G8" t="n">
         <v>-3.5114</v>
@@ -1078,13 +1078,13 @@
         <v>4.1514</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.3563</v>
+        <v>-0.4618</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.4398</v>
+        <v>-0.7305</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0835</v>
+        <v>0.2687</v>
       </c>
       <c r="V8" t="n">
         <v>1.2452</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.769</v>
+        <v>-2.6896</v>
       </c>
       <c r="E9" t="n">
         <v>-1.5687</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.2003</v>
+        <v>-1.1209</v>
       </c>
       <c r="G9" t="n">
         <v>-2.4692</v>
@@ -1156,13 +1156,13 @@
         <v>0.1887</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.4885</v>
+        <v>-0.4092</v>
       </c>
       <c r="T9" t="n">
         <v>-0.3404</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1481</v>
+        <v>-0.0688</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,22 +1189,22 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>1.845799999999999</v>
+        <v>3.315700000000001</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.5619</v>
+        <v>-2.0921</v>
       </c>
       <c r="F10" t="n">
-        <v>5.4076</v>
+        <v>5.407699999999998</v>
       </c>
       <c r="G10" t="n">
         <v>-7.6601</v>
       </c>
       <c r="H10" t="n">
-        <v>-6.9025</v>
+        <v>-6.902500000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.7575</v>
+        <v>-0.7575000000000003</v>
       </c>
       <c r="J10" t="n">
         <v>8.244</v>
@@ -1234,10 +1234,10 @@
         <v>23.5875</v>
       </c>
       <c r="S10" t="n">
-        <v>-5.476</v>
+        <v>-4.0064</v>
       </c>
       <c r="T10" t="n">
-        <v>-6.9166</v>
+        <v>-5.447</v>
       </c>
       <c r="U10" t="n">
         <v>1.4407</v>
@@ -1246,10 +1246,10 @@
         <v>3.6596</v>
       </c>
       <c r="W10" t="n">
-        <v>7.3762</v>
+        <v>7.376200000000001</v>
       </c>
       <c r="X10" t="n">
-        <v>-3.716600000000001</v>
+        <v>-3.7166</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>4.2898</v>
+        <v>3.5512</v>
       </c>
       <c r="E11" t="n">
-        <v>4.2284</v>
+        <v>3.2541</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0614</v>
+        <v>0.2972</v>
       </c>
       <c r="G11" t="n">
         <v>3.8002</v>
@@ -1312,13 +1312,13 @@
         <v>0.7548</v>
       </c>
       <c r="S11" t="n">
-        <v>1.9234</v>
+        <v>1.1848</v>
       </c>
       <c r="T11" t="n">
-        <v>1.4196</v>
+        <v>0.4453</v>
       </c>
       <c r="U11" t="n">
-        <v>0.5038</v>
+        <v>0.7396</v>
       </c>
       <c r="V11" t="n">
         <v>-2.1886</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>3.4828</v>
+        <v>3.1701</v>
       </c>
       <c r="E12" t="n">
-        <v>2.1248</v>
+        <v>1.7351</v>
       </c>
       <c r="F12" t="n">
-        <v>1.358</v>
+        <v>1.435</v>
       </c>
       <c r="G12" t="n">
         <v>2.457</v>
@@ -1390,13 +1390,13 @@
         <v>0.1887</v>
       </c>
       <c r="S12" t="n">
-        <v>0.8371</v>
+        <v>0.5244</v>
       </c>
       <c r="T12" t="n">
-        <v>0.4144</v>
+        <v>0.0247</v>
       </c>
       <c r="U12" t="n">
-        <v>0.4227</v>
+        <v>0.4997</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>2.091</v>
+        <v>2.3943</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.2712</v>
+        <v>0.1185</v>
       </c>
       <c r="F13" t="n">
-        <v>2.3623</v>
+        <v>2.2758</v>
       </c>
       <c r="G13" t="n">
         <v>1.1149</v>
@@ -1468,13 +1468,13 @@
         <v>2.2644</v>
       </c>
       <c r="S13" t="n">
-        <v>1.3163</v>
+        <v>1.6196</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.6902</v>
+        <v>-0.3005</v>
       </c>
       <c r="U13" t="n">
-        <v>2.0065</v>
+        <v>1.92</v>
       </c>
       <c r="V13" t="n">
         <v>2.4904</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.5152</v>
+        <v>2.0456</v>
       </c>
       <c r="E14" t="n">
-        <v>1.0351</v>
+        <v>1.3274</v>
       </c>
       <c r="F14" t="n">
-        <v>0.4801</v>
+        <v>0.7181999999999999</v>
       </c>
       <c r="G14" t="n">
         <v>0.2815</v>
@@ -1546,13 +1546,13 @@
         <v>1.3209</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.3704</v>
+        <v>0.16</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.7055</v>
+        <v>-0.4131</v>
       </c>
       <c r="U14" t="n">
-        <v>0.3351</v>
+        <v>0.5732</v>
       </c>
       <c r="V14" t="n">
         <v>0.6606</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.2813</v>
+        <v>0.6752</v>
       </c>
       <c r="E15" t="n">
-        <v>0.307</v>
+        <v>-0.0827</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9743000000000001</v>
+        <v>0.7579</v>
       </c>
       <c r="G15" t="n">
         <v>2.4188</v>
@@ -1624,13 +1624,13 @@
         <v>1.3209</v>
       </c>
       <c r="S15" t="n">
-        <v>1.9194</v>
+        <v>1.3133</v>
       </c>
       <c r="T15" t="n">
-        <v>0.5472</v>
+        <v>0.1575</v>
       </c>
       <c r="U15" t="n">
-        <v>1.3722</v>
+        <v>1.1558</v>
       </c>
       <c r="V15" t="n">
         <v>0.3398</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.1063</v>
+        <v>0.6286</v>
       </c>
       <c r="E16" t="n">
-        <v>-2.4738</v>
+        <v>-2.1815</v>
       </c>
       <c r="F16" t="n">
-        <v>2.3675</v>
+        <v>2.8102</v>
       </c>
       <c r="G16" t="n">
         <v>1.7112</v>
@@ -1702,13 +1702,13 @@
         <v>2.0757</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2581</v>
+        <v>0.993</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.7026</v>
+        <v>-0.4103</v>
       </c>
       <c r="U16" t="n">
-        <v>0.9606</v>
+        <v>1.4033</v>
       </c>
       <c r="V16" t="n">
         <v>-0.9434</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.6188</v>
+        <v>-0.5394</v>
       </c>
       <c r="E17" t="n">
         <v>0.7308</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.3496</v>
+        <v>-1.2702</v>
       </c>
       <c r="G17" t="n">
         <v>-0.4998</v>
@@ -1780,13 +1780,13 @@
         <v>0.1887</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.0059</v>
+        <v>0.0735</v>
       </c>
       <c r="T17" t="n">
         <v>0.0123</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0182</v>
+        <v>0.0611</v>
       </c>
       <c r="V17" t="n">
         <v>-0.3018</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.9063</v>
+        <v>-0.7829</v>
       </c>
       <c r="E18" t="n">
-        <v>-4.2921</v>
+        <v>-3.9024</v>
       </c>
       <c r="F18" t="n">
-        <v>2.3859</v>
+        <v>3.1195</v>
       </c>
       <c r="G18" t="n">
         <v>-1.2676</v>
@@ -1858,13 +1858,13 @@
         <v>1.887</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.9029</v>
+        <v>0.2205</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.1758</v>
+        <v>-0.786</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2728</v>
+        <v>1.0065</v>
       </c>
       <c r="V18" t="n">
         <v>-0.3018</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.2554</v>
+        <v>-2.0401</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.9933999999999999</v>
+        <v>-1.0908</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.262</v>
+        <v>-0.9493</v>
       </c>
       <c r="G19" t="n">
         <v>0.3174</v>
@@ -1936,13 +1936,13 @@
         <v>1.5096</v>
       </c>
       <c r="S19" t="n">
-        <v>0.2951</v>
+        <v>0.5104</v>
       </c>
       <c r="T19" t="n">
-        <v>0.0029</v>
+        <v>-0.0945</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2922</v>
+        <v>0.6049</v>
       </c>
       <c r="V19" t="n">
         <v>-1.547</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.6813</v>
+        <v>-2.5225</v>
       </c>
       <c r="E20" t="n">
         <v>-1.3609</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.3204</v>
+        <v>-1.1617</v>
       </c>
       <c r="G20" t="n">
         <v>-0.361</v>
@@ -2014,13 +2014,13 @@
         <v>0.3774</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.1881</v>
+        <v>-0.0294</v>
       </c>
       <c r="T20" t="n">
         <v>-0.164</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0241</v>
+        <v>0.1346</v>
       </c>
       <c r="V20" t="n">
         <v>-0.6226</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-6.9379</v>
+        <v>-6.4772</v>
       </c>
       <c r="E21" t="n">
-        <v>-4.4423</v>
+        <v>-3.9552</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.4956</v>
+        <v>-2.522</v>
       </c>
       <c r="G21" t="n">
         <v>-2.3126</v>
@@ -2092,13 +2092,13 @@
         <v>0.3774</v>
       </c>
       <c r="S21" t="n">
-        <v>0.3939</v>
+        <v>0.8546</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.3992</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="U21" t="n">
-        <v>0.7931</v>
+        <v>0.7665999999999999</v>
       </c>
       <c r="V21" t="n">
         <v>-1.2452</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.845899999999999</v>
+        <v>0.1029000000000027</v>
       </c>
       <c r="E22" t="n">
-        <v>-5.407600000000001</v>
+        <v>-5.4076</v>
       </c>
       <c r="F22" t="n">
-        <v>3.5619</v>
+        <v>5.510600000000002</v>
       </c>
       <c r="G22" t="n">
         <v>7.659999999999997</v>
@@ -2170,13 +2170,13 @@
         <v>12.2655</v>
       </c>
       <c r="S22" t="n">
-        <v>5.476</v>
+        <v>7.4247</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.4409</v>
+        <v>-1.4406</v>
       </c>
       <c r="U22" t="n">
-        <v>6.916700000000001</v>
+        <v>8.8653</v>
       </c>
       <c r="V22" t="n">
         <v>-3.6596</v>
